--- a/artfynd/A 47058-2023 artfynd.xlsx
+++ b/artfynd/A 47058-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 47058-2023 artfynd.xlsx
+++ b/artfynd/A 47058-2023 artfynd.xlsx
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 47058-2023 artfynd.xlsx
+++ b/artfynd/A 47058-2023 artfynd.xlsx
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 47058-2023 artfynd.xlsx
+++ b/artfynd/A 47058-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66138627</v>
+        <v>69751192</v>
       </c>
       <c r="B2" t="n">
-        <v>96979</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99156</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>219875</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Borgmästarskogen - Privat område, ej kommunal mark, Vg</t>
+          <t>Lilla Åsbotorp - Telemast norr om, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>430742</v>
+        <v>430660</v>
       </c>
       <c r="R2" t="n">
-        <v>6475306</v>
+        <v>6475444</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,17 +749,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-06-04</t>
+          <t>2017-07-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-06-04</t>
+          <t>2017-07-15</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Granskog, sumpskog och mindre skogsbäck</t>
+          <t>Privat tomtmark, betesmark, väg, vägdiken och blandskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,15 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>66138628</v>
+        <v>69908703</v>
       </c>
       <c r="B3" t="n">
-        <v>98005</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99156</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,46 +801,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220093</v>
+        <v>219875</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Borgmästarskogen - Privat område, ej kommunal mark, Vg</t>
+          <t>Lilla Åsbotorp väster om, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>430802</v>
+        <v>430422</v>
       </c>
       <c r="R3" t="n">
-        <v>6475345</v>
+        <v>6475478</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,17 +855,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-06-04</t>
+          <t>2015-11-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-06-04</t>
+          <t>2015-11-21</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Granskog, sumpskog och mindre skogsbäck</t>
+          <t>Objekt 455 i Skövde kn skogsbruksplan</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,15 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>69908703</v>
+        <v>95383805</v>
       </c>
       <c r="B4" t="n">
-        <v>98138</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99156</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -942,17 +927,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lilla Åsbotorp väster om, Vg</t>
+          <t>Lilla Åsbotorp, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>430422</v>
+        <v>430669</v>
       </c>
       <c r="R4" t="n">
-        <v>6475478</v>
+        <v>6475480</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,17 +961,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2015-11-21</t>
+          <t>2021-08-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2015-11-21</t>
+          <t>2021-08-07</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Objekt 455 i Skövde kn skogsbruksplan</t>
+          <t>Ödetomt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,23 +994,14 @@
           <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Billingens flora</t>
-        </is>
-      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>69908707</v>
+        <v>87985606</v>
       </c>
       <c r="B5" t="n">
-        <v>96979</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107719</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1033,16 +1009,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>220015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Hässleklocka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Campanula latifolia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1053,17 +1029,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lilla Åsbotorp väster om, Vg</t>
+          <t>Telemasten Billingen, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>430422</v>
+        <v>430663</v>
       </c>
       <c r="R5" t="n">
-        <v>6475478</v>
+        <v>6475413</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1087,17 +1063,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2015-11-21</t>
+          <t>2007-07-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2015-11-21</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Objekt 455 i Skövde kn skogsbruksplan</t>
+          <t>2007-07-06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,23 +1079,470 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Barrskog, betesmark, vägkanter</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>66138628</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Borgmästarskogen - Privat område, ej kommunal mark, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>430802</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6475345</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2017-06-04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2017-06-04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Granskog, sumpskog och mindre skogsbäck</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Rolf-Göran Carlsson</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
+      <c r="AY6" t="inlineStr">
         <is>
           <t>Billingens flora</t>
         </is>
       </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>66138627</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Borgmästarskogen - Privat område, ej kommunal mark, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>430742</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6475306</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2017-06-04</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2017-06-04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Granskog, sumpskog och mindre skogsbäck</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>69908707</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lilla Åsbotorp väster om, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>430422</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6475478</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2015-11-21</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2015-11-21</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Objekt 455 i Skövde kn skogsbruksplan</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>95383808</v>
+      </c>
+      <c r="B9" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lilla Åsbotorp, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>430636</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6475501</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-08-07</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-08-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ödetomt</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47058-2023 artfynd.xlsx
+++ b/artfynd/A 47058-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69751192</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -893,6 +903,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69908703</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95383805</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1101,6 +1121,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87985606</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1216,6 +1241,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66138628</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1322,6 +1352,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66138627</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1428,6 +1463,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69908707</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1543,8 +1583,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95383808</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>